--- a/outputs/external_validation/external_validation_metrics.xlsx
+++ b/outputs/external_validation/external_validation_metrics.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,22 +429,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
@@ -445,7 +457,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7988393552116125</v>
+        <v>0.8000088320523371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -465,7 +477,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4609817448290185</v>
+        <v>0.4596397991762687</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -485,7 +497,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2897017854978407</v>
+        <v>0.2882966457846711</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -505,7 +517,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.800909237610455</v>
+        <v>0.8020666808870048</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -525,7 +537,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7988393552116125</v>
+        <v>0.8000088320523371</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -545,7 +557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8452580317718827</v>
+        <v>0.8461576468448078</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -565,7 +577,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8803671700200552</v>
+        <v>0.8877279806716551</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -585,7 +597,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5814957467602162</v>
+        <v>0.6515985820035656</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -594,7 +606,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -605,7 +617,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7579231833244402</v>
+        <v>0.7979065794914906</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -625,7 +637,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6697094650423282</v>
+        <v>0.7247525807475281</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -645,7 +657,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.176427436564224</v>
+        <v>0.146307997487925</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -665,7 +677,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7279232433569645</v>
+        <v>0.7686988978675616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -685,7 +697,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8015972488934877</v>
+        <v>0.8049418697189394</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -705,7 +717,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9523438277962404</v>
+        <v>0.9462316023913716</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -725,7 +737,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.020478104011452</v>
+        <v>1.027571509496141</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -745,7 +757,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08877393357249205</v>
+        <v>0.03913698565608728</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -765,7 +777,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.003452375829862079</v>
+        <v>0.0061662290076813</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
